--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,17 +565,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>22868653.3</v>
+        <v>26529.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1208066-75-CM26</t>
+          <t>3453-51-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,53 +590,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6985216.7</v>
+        <v>20487.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3453-51-CM26</t>
+          <t>1456839-6-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.981.420-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,28 +676,28 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17660790</v>
+        <v>6744.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1456839-6-CM26</t>
+          <t>1389183-36-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.981.420-7</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,28 +737,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5814049.92</v>
+        <v>48085.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1389183-36-CM26</t>
+          <t>5621-56-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,28 +798,28 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>41450325.84</v>
+        <v>6740.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5621-56-CM26</t>
+          <t>1475044-20-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -859,28 +859,28 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.007.474-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5810258.3</v>
+        <v>44990.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1475044-20-CM26</t>
+          <t>1475044-22-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -920,28 +920,28 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38782366.2</v>
+        <v>40524.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1475044-22-CM26</t>
+          <t>2446-154-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,53 +956,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>34932678.65</v>
+        <v>12586.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2446-154-CM26</t>
+          <t>3453-53-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,53 +1017,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10849440.8</v>
+        <v>6112.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3453-53-CM26</t>
+          <t>3714-24-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,43 +1088,43 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.205.938-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5269409.25</v>
+        <v>23228.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3714-24-CM26</t>
+          <t>1079713-50-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,43 +1149,43 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>53.322.604-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>20023235</v>
+        <v>31068.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1079713-50-CM26</t>
+          <t>542429-3-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,43 +1210,43 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53.322.604-3</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>26781834</v>
+        <v>6866.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>542429-3-CM26</t>
+          <t>2450-122-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,43 +1271,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5919200</v>
+        <v>16458.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2450-122-CM26</t>
+          <t>3081-5-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,43 +1332,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>INVERSIONES JIMENEZ SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.316.878-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>14187348.28</v>
+        <v>8613.200000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3081-5-CM26</t>
+          <t>2467-56-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,53 +1383,53 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>INVERSIONES JIMENEZ SPA</t>
+          <t>DISTRIBUIDORA MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.316.878-4</t>
+          <t>77.208.692-K</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7424750.7</v>
+        <v>9275.780000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2467-56-CM26</t>
+          <t>1475044-26-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,53 +1444,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MUEBLES ASENJO LIMITADA</t>
+          <t>BODEGA STOCK SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.208.692-K</t>
+          <t>76.744.548-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7995907.5</v>
+        <v>9839.450000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1475044-26-CM26</t>
+          <t>1460278-56-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,28 +1530,28 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>BODEGA STOCK SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.744.548-2</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8481805.75</v>
+        <v>15396.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>886182-44-CM26</t>
+          <t>1233615-74-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,28 +1591,28 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>OFISILLAS CHILE SPA</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.855.435-8</t>
+          <t>77.205.938-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6120000</v>
+        <v>12721.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1460278-56-CM26</t>
+          <t>1475044-27-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13271992.65</v>
+        <v>34546.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1233615-74-CM26</t>
+          <t>1082957-46-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>62.000.680-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10966328.38</v>
+        <v>9310.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1475044-27-CM26</t>
+          <t>3714-33-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,43 +1759,43 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>29779750</v>
+        <v>6397.29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1082957-46-CM26</t>
+          <t>1057049-11798-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.680-7</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1835,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8026252.5</v>
+        <v>13838.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3714-33-CM26</t>
+          <t>1057973-1-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,53 +1871,53 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5514593.45</v>
+        <v>13226.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057049-11798-CM26</t>
+          <t>1456838-11-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.981.440-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,28 +1957,28 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>11928710.92</v>
+        <v>6726.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057973-1-CM26</t>
+          <t>1375757-57-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,28 +2018,28 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>11401228.05</v>
+        <v>39097.12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1456838-11-CM26</t>
+          <t>5684-100-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.981.440-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,28 +2079,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>5798596.3</v>
+        <v>10846.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1375757-57-CM26</t>
+          <t>4803-61-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,48 +2120,48 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.007.474-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>33702500</v>
+        <v>15049.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5684-100-CM26</t>
+          <t>1305525-31-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.120-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,28 +2201,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9350000</v>
+        <v>35519.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4803-61-CM26</t>
+          <t>2378-55-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,169 +2237,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>12973183.2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1305525-31-CM26</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>61.981.120-8</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>STATUS SPA</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>30618249.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2378-55-CM26</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>69.070.700-4</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>JUEGOS MAGICOS</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>24269523.6</v>
+        <v>28154.25</v>
       </c>
     </row>
   </sheetData>
